--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -752,60 +752,100 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via Medicaid clause</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>7969.047577547774</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only clause (300% FPL)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Eligible families (weighted)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>7340</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Expected recipients / year</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>16494.01591410528</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>7903.382625508781</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  via Medicaid clause</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only clause (300% FPL)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Expected recipients / year</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>16494.01591410528</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>7903.382625508781</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Expected infants (postnatal)</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B38" s="6" t="n">
         <v>8590.6332885965</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Avg benefit per recipient</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B39" s="6" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -903,7 +943,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57024</v>
+        <v>57028</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
@@ -978,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>334084</v>
+        <v>334087</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>110343</v>
@@ -1007,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1016,6 +1056,11 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1046,6 +1091,31 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  via Medicaid ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Births served</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via Medicaid</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
           <t>Expected recipients</t>
         </is>
       </c>
@@ -1069,6 +1139,21 @@
         <v>1812020</v>
       </c>
       <c r="F2" s="11" t="n">
+        <v>4863875</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>1723</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="11" t="n">
         <v>3567</v>
       </c>
     </row>
@@ -1091,6 +1176,21 @@
         <v>3051965</v>
       </c>
       <c r="F3" s="11" t="n">
+        <v>14856311</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>5790</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>5264</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="11" t="n">
         <v>10895</v>
       </c>
     </row>
@@ -1113,6 +1213,21 @@
         <v>1018361</v>
       </c>
       <c r="F4" s="11" t="n">
+        <v>1605760</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11" t="n">
         <v>1178</v>
       </c>
     </row>
@@ -1135,6 +1250,21 @@
         <v>631452</v>
       </c>
       <c r="F5" s="11" t="n">
+        <v>1165894</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>454</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>413</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11" t="n">
         <v>855</v>
       </c>
     </row>
@@ -1149,10 +1279,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1166,6 +1296,12 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,6 +1382,36 @@
           <t>First-year ($)</t>
         </is>
       </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
+          <t>Eligible families</t>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via Medicaid</t>
+        </is>
+      </c>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only</t>
+        </is>
+      </c>
+      <c r="R2" s="9" t="inlineStr">
+        <is>
+          <t>Births served</t>
+        </is>
+      </c>
+      <c r="S2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via Medicaid</t>
+        </is>
+      </c>
+      <c r="T2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1294,6 +1460,24 @@
       <c r="N3" s="11" t="n">
         <v>12357387</v>
       </c>
+      <c r="O3" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="Q3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>8766</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>7969</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1342,6 +1526,24 @@
       <c r="N4" s="11" t="n">
         <v>15608703</v>
       </c>
+      <c r="O4" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>8766</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>7969</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1390,6 +1592,24 @@
       <c r="N5" s="11" t="n">
         <v>25909510</v>
       </c>
+      <c r="O5" s="11" t="n">
+        <v>11521</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="Q5" s="11" t="n">
+        <v>4181</v>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>14551</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>7969</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>5259</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1437,6 +1657,24 @@
       </c>
       <c r="N6" s="11" t="n">
         <v>28682275</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>11521</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>7340</v>
+      </c>
+      <c r="Q6" s="11" t="n">
+        <v>4181</v>
+      </c>
+      <c r="R6" s="11" t="n">
+        <v>14551</v>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>7969</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>5259</v>
       </c>
     </row>
   </sheetData>
@@ -1450,16 +1688,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1495,6 +1738,31 @@
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  via Medicaid ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only ($)</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Births served</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via Medicaid</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  via income-only</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
           <t>Expected recipients</t>
         </is>
       </c>
@@ -1523,6 +1791,21 @@
         <v>1812020</v>
       </c>
       <c r="G2" s="11" t="n">
+        <v>4863875</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>1723</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="n">
         <v>3567</v>
       </c>
     </row>
@@ -1550,6 +1833,21 @@
         <v>3051965</v>
       </c>
       <c r="G3" s="11" t="n">
+        <v>14856311</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>5790</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>5264</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11" t="n">
         <v>10895</v>
       </c>
     </row>
@@ -1577,6 +1875,21 @@
         <v>1018361</v>
       </c>
       <c r="G4" s="11" t="n">
+        <v>1605760</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>1178</v>
       </c>
     </row>
@@ -1604,6 +1917,21 @@
         <v>631452</v>
       </c>
       <c r="G5" s="11" t="n">
+        <v>1165894</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>454</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>413</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11" t="n">
         <v>855</v>
       </c>
     </row>
@@ -1631,6 +1959,21 @@
         <v>2755780</v>
       </c>
       <c r="G6" s="11" t="n">
+        <v>7397143</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>1723</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="n">
         <v>3567</v>
       </c>
     </row>
@@ -1658,6 +2001,21 @@
         <v>4641530</v>
       </c>
       <c r="G7" s="11" t="n">
+        <v>22593973</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>5790</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>5264</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11" t="n">
         <v>10895</v>
       </c>
     </row>
@@ -1685,6 +2043,21 @@
         <v>1548757</v>
       </c>
       <c r="G8" s="11" t="n">
+        <v>2442094</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11" t="n">
         <v>1178</v>
       </c>
     </row>
@@ -1712,6 +2085,21 @@
         <v>960333</v>
       </c>
       <c r="G9" s="11" t="n">
+        <v>1773130</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>454</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>413</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>855</v>
       </c>
     </row>
@@ -1739,6 +2127,21 @@
         <v>2755780</v>
       </c>
       <c r="G10" s="11" t="n">
+        <v>7397143</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>1723</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <v>3567</v>
       </c>
     </row>
@@ -1766,6 +2169,21 @@
         <v>6925251</v>
       </c>
       <c r="G11" s="11" t="n">
+        <v>22593973</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>18056127</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>10417</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>5264</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>4207</v>
+      </c>
+      <c r="L11" s="11" t="n">
         <v>19601</v>
       </c>
     </row>
@@ -1793,6 +2211,21 @@
         <v>1548757</v>
       </c>
       <c r="G12" s="11" t="n">
+        <v>2442094</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="11" t="n">
         <v>1178</v>
       </c>
     </row>
@@ -1820,6 +2253,21 @@
         <v>3499931</v>
       </c>
       <c r="G13" s="11" t="n">
+        <v>1773130</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>4518002</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>1612</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>413</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <v>3034</v>
       </c>
     </row>
@@ -1847,6 +2295,21 @@
         <v>4643300</v>
       </c>
       <c r="G14" s="11" t="n">
+        <v>12463680</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>1723</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="n">
         <v>3567</v>
       </c>
     </row>
@@ -1874,6 +2337,21 @@
         <v>11668574</v>
       </c>
       <c r="G15" s="11" t="n">
+        <v>38069297</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>30423337</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>10417</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>5264</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>4207</v>
+      </c>
+      <c r="L15" s="11" t="n">
         <v>19601</v>
       </c>
     </row>
@@ -1901,6 +2379,21 @@
         <v>2609549</v>
       </c>
       <c r="G16" s="11" t="n">
+        <v>4114761</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>569</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11" t="n">
         <v>1178</v>
       </c>
     </row>
@@ -1928,6 +2421,21 @@
         <v>5897144</v>
       </c>
       <c r="G17" s="11" t="n">
+        <v>2987602</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>7612523</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>1612</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>413</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L17" s="11" t="n">
         <v>3034</v>
       </c>
     </row>
